--- a/reports/pdf_rolling5_20260928.xlsx
+++ b/reports/pdf_rolling5_20260928.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,927억   ·   현금 37억(0.7%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 15종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,927억   ·   현금 18억(0.4%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 15종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-292543165</v>
+        <v>-635032723</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.92%</t>
+          <t>0.71%→0.50%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-635032723</v>
+        <v>-292543165</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.50%</t>
+          <t>1.05%→0.92%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-633348023</v>
+        <v>-2237182229</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.77%</t>
+          <t>1.61%→0.98%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>49→42</t>
+          <t>22→15</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2237182229</v>
+        <v>-633348023</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.61%→0.98%</t>
+          <t>0.98%→0.77%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>22→15</t>
+          <t>49→42</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,285억   ·   현금 118억(3.5%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,285억   ·   현금 59억(1.8%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1491,7 +1491,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,689억   ·   현금 87억(3.2%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 1종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,689억   ·   현금 44억(1.6%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1680,7 +1680,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,999억   ·   현금 71억(3.5%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,999억   ·   현금 35억(1.8%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1973,7 +1973,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 299억   ·   현금 2억(0.8%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 9종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 299억   ·   현금 1억(0.4%)      오늘 2026-09-28  vs  5일전 2026-09-17      매수 9종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2215,23 +2215,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-33389990</v>
+        <v>-26249992</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.70%→2.59%</t>
+          <t>0.18%→0.09%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>31→16</t>
         </is>
       </c>
     </row>
@@ -2259,23 +2259,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-26249992</v>
+        <v>-33389990</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.09%</t>
+          <t>2.70%→2.59%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>31→16</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-56153984</v>
+        <v>-62789982</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>2.85%→2.64%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-62789982</v>
+        <v>-56153984</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.64%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260928.xlsx
+++ b/reports/pdf_rolling5_20260928.xlsx
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-880800693</v>
+        <v>-2725249670</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.77%→1.92%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2725249670</v>
+        <v>-880800693</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.77%→1.92%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2237182229</v>
+        <v>-633348023</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.61%→0.98%</t>
+          <t>0.98%→0.77%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>22→15</t>
+          <t>49→42</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-633348023</v>
+        <v>-2237182229</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.77%</t>
+          <t>1.61%→0.98%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>49→42</t>
+          <t>22→15</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2435,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-34271990</v>
+        <v>-62789982</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>2.85%→2.64%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-62789982</v>
+        <v>-56153984</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.64%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-56153984</v>
+        <v>-34271990</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260928.xlsx
+++ b/reports/pdf_rolling5_20260928.xlsx
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2725249670</v>
+        <v>-880800693</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>2.77%→1.92%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-880800693</v>
+        <v>-2725249670</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.77%→1.92%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-635032723</v>
+        <v>-292543165</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.50%</t>
+          <t>1.05%→0.92%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-292543165</v>
+        <v>-635032723</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.92%</t>
+          <t>0.71%→0.50%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -2215,23 +2215,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-26249992</v>
+        <v>-33389990</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.09%</t>
+          <t>2.70%→2.59%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>31→16</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2259,23 +2259,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-33389990</v>
+        <v>-26249992</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.70%→2.59%</t>
+          <t>0.18%→0.09%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>31→16</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-56153984</v>
+        <v>-34271990</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.26%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-34271990</v>
+        <v>-56153984</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>2.45%→2.26%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260928.xlsx
+++ b/reports/pdf_rolling5_20260928.xlsx
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-880800693</v>
+        <v>-2725249670</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.49%</t>
+          <t>2.77%→1.92%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2725249670</v>
+        <v>-880800693</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.77%→1.92%</t>
+          <t>0.75%→0.49%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -2215,23 +2215,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-33389990</v>
+        <v>-26249992</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.70%→2.59%</t>
+          <t>0.18%→0.09%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>31→16</t>
         </is>
       </c>
     </row>
@@ -2259,23 +2259,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-26249992</v>
+        <v>-33389990</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.09%</t>
+          <t>2.70%→2.59%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>31→16</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2435,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-62789982</v>
+        <v>-34271990</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.64%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-34271990</v>
+        <v>-62789982</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>2.85%→2.64%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
